--- a/summary/NPL/NPL_EWS_export.xlsx
+++ b/summary/NPL/NPL_EWS_export.xlsx
@@ -7,14 +7,17 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Competencies" sheetId="1" r:id="rId1"/>
-    <sheet name="Values" sheetId="2" r:id="rId2"/>
-    <sheet name="Extra_questions" sheetId="3" r:id="rId3"/>
-    <sheet name="Trust Index" sheetId="4" r:id="rId4"/>
-    <sheet name="Sampling_age" sheetId="5" r:id="rId5"/>
-    <sheet name="Sampling_Gender" sheetId="6" r:id="rId6"/>
-    <sheet name="Sampling_Geo" sheetId="7" r:id="rId7"/>
-    <sheet name="Sampling_type" sheetId="8" r:id="rId8"/>
+    <sheet name="Pillar1" sheetId="1" r:id="rId1"/>
+    <sheet name="Pillar2" sheetId="2" r:id="rId2"/>
+    <sheet name="Pillar3" sheetId="3" r:id="rId3"/>
+    <sheet name="Pillar4" sheetId="4" r:id="rId4"/>
+    <sheet name="Extra_questions" sheetId="5" r:id="rId5"/>
+    <sheet name="Index by profile" sheetId="6" r:id="rId6"/>
+    <sheet name="Index by factors" sheetId="7" r:id="rId7"/>
+    <sheet name="Sampling_age" sheetId="8" r:id="rId8"/>
+    <sheet name="Sampling_Gender" sheetId="9" r:id="rId9"/>
+    <sheet name="Sampling_Geo" sheetId="10" r:id="rId10"/>
+    <sheet name="Sampling_type" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -358,7 +361,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,14 +394,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Don’t know</t>
+          <t>Yes completely</t>
         </is>
       </c>
       <c r="C2">
-        <v>576</v>
+        <v>133</v>
       </c>
       <c r="D2">
-        <v>17.58778625954199</v>
+        <v>7.902554961378491</v>
       </c>
     </row>
     <row r="3">
@@ -413,10 +416,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>1219</v>
+        <v>841</v>
       </c>
       <c r="D3">
-        <v>37.22137404580153</v>
+        <v>49.97029114676174</v>
       </c>
     </row>
     <row r="4">
@@ -427,14 +430,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Not at all</t>
+          <t>Not so much</t>
         </is>
       </c>
       <c r="C4">
-        <v>219</v>
+        <v>423</v>
       </c>
       <c r="D4">
-        <v>6.687022900763359</v>
+        <v>25.13368983957219</v>
       </c>
     </row>
     <row r="5">
@@ -445,14 +448,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Not so much</t>
+          <t>Not at all</t>
         </is>
       </c>
       <c r="C5">
-        <v>743</v>
+        <v>98</v>
       </c>
       <c r="D5">
-        <v>22.68702290076336</v>
+        <v>5.822935234699941</v>
       </c>
     </row>
     <row r="6">
@@ -463,14 +466,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Yes, completely</t>
+          <t>Don’t know</t>
         </is>
       </c>
       <c r="C6">
-        <v>518</v>
+        <v>188</v>
       </c>
       <c r="D6">
-        <v>15.81679389312977</v>
+        <v>11.17052881758764</v>
       </c>
     </row>
     <row r="7">
@@ -481,14 +484,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Don’t know</t>
+          <t>Yes completely</t>
         </is>
       </c>
       <c r="C7">
-        <v>429</v>
+        <v>173</v>
       </c>
       <c r="D7">
-        <v>13.09923664122137</v>
+        <v>10.27926322043969</v>
       </c>
     </row>
     <row r="8">
@@ -503,10 +506,10 @@
         </is>
       </c>
       <c r="C8">
-        <v>1503</v>
+        <v>824</v>
       </c>
       <c r="D8">
-        <v>45.89312977099237</v>
+        <v>48.96019013666073</v>
       </c>
     </row>
     <row r="9">
@@ -517,14 +520,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Not at all</t>
+          <t>Not so much</t>
         </is>
       </c>
       <c r="C9">
-        <v>104</v>
+        <v>410</v>
       </c>
       <c r="D9">
-        <v>3.17557251908397</v>
+        <v>24.3612596553773</v>
       </c>
     </row>
     <row r="10">
@@ -535,14 +538,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Not so much</t>
+          <t>Not at all</t>
         </is>
       </c>
       <c r="C10">
-        <v>445</v>
+        <v>104</v>
       </c>
       <c r="D10">
-        <v>13.58778625954198</v>
+        <v>6.179441473559121</v>
       </c>
     </row>
     <row r="11">
@@ -553,14 +556,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yes, completely</t>
+          <t>Don’t know</t>
         </is>
       </c>
       <c r="C11">
-        <v>794</v>
+        <v>172</v>
       </c>
       <c r="D11">
-        <v>24.24427480916031</v>
+        <v>10.21984551396316</v>
       </c>
     </row>
     <row r="12">
@@ -571,14 +574,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Don’t know</t>
+          <t>Yes completely</t>
         </is>
       </c>
       <c r="C12">
-        <v>498</v>
+        <v>230</v>
       </c>
       <c r="D12">
-        <v>15.20610687022901</v>
+        <v>13.6660724896019</v>
       </c>
     </row>
     <row r="13">
@@ -593,10 +596,10 @@
         </is>
       </c>
       <c r="C13">
-        <v>1417</v>
+        <v>914</v>
       </c>
       <c r="D13">
-        <v>43.26717557251909</v>
+        <v>54.30778371954843</v>
       </c>
     </row>
     <row r="14">
@@ -607,14 +610,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Not at all</t>
+          <t>Not so much</t>
         </is>
       </c>
       <c r="C14">
-        <v>190</v>
+        <v>328</v>
       </c>
       <c r="D14">
-        <v>5.801526717557252</v>
+        <v>19.48900772430184</v>
       </c>
     </row>
     <row r="15">
@@ -625,14 +628,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Not so much</t>
+          <t>Not at all</t>
         </is>
       </c>
       <c r="C15">
-        <v>543</v>
+        <v>82</v>
       </c>
       <c r="D15">
-        <v>16.58015267175572</v>
+        <v>4.87225193107546</v>
       </c>
     </row>
     <row r="16">
@@ -643,38 +646,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Yes, completely</t>
+          <t>Don’t know</t>
         </is>
       </c>
       <c r="C16">
-        <v>627</v>
+        <v>129</v>
       </c>
       <c r="D16">
-        <v>19.14503816793893</v>
+        <v>7.66488413547237</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Inclusiveness</t>
+          <t>Inclusiness</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Don’t know</t>
+          <t>Yes completely</t>
         </is>
       </c>
       <c r="C17">
-        <v>511</v>
+        <v>141</v>
       </c>
       <c r="D17">
-        <v>15.6030534351145</v>
+        <v>8.377896613190732</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Inclusiveness</t>
+          <t>Inclusiness</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -683,64 +686,64 @@
         </is>
       </c>
       <c r="C18">
-        <v>1295</v>
+        <v>758</v>
       </c>
       <c r="D18">
-        <v>39.54198473282442</v>
+        <v>45.03862150920974</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Inclusiveness</t>
+          <t>Inclusiness</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Not at all</t>
+          <t>Not so much</t>
         </is>
       </c>
       <c r="C19">
-        <v>138</v>
+        <v>488</v>
       </c>
       <c r="D19">
-        <v>4.213740458015267</v>
+        <v>28.99584076054664</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Inclusiveness</t>
+          <t>Inclusiness</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Not so much</t>
+          <t>Not at all</t>
         </is>
       </c>
       <c r="C20">
-        <v>531</v>
+        <v>86</v>
       </c>
       <c r="D20">
-        <v>16.21374045801527</v>
+        <v>5.109922756981581</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Inclusiveness</t>
+          <t>Inclusiness</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Yes, completely</t>
+          <t>Don’t know</t>
         </is>
       </c>
       <c r="C21">
-        <v>800</v>
+        <v>210</v>
       </c>
       <c r="D21">
-        <v>24.42748091603053</v>
+        <v>12.4777183600713</v>
       </c>
     </row>
     <row r="22">
@@ -751,14 +754,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Don’t know</t>
+          <t>Yes completely</t>
         </is>
       </c>
       <c r="C22">
-        <v>959</v>
+        <v>103</v>
       </c>
       <c r="D22">
-        <v>29.2824427480916</v>
+        <v>6.120023767082591</v>
       </c>
     </row>
     <row r="23">
@@ -773,10 +776,10 @@
         </is>
       </c>
       <c r="C23">
-        <v>974</v>
+        <v>732</v>
       </c>
       <c r="D23">
-        <v>29.74045801526717</v>
+        <v>43.49376114081996</v>
       </c>
     </row>
     <row r="24">
@@ -787,14 +790,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Not at all</t>
+          <t>Not so much</t>
         </is>
       </c>
       <c r="C24">
-        <v>301</v>
+        <v>506</v>
       </c>
       <c r="D24">
-        <v>9.190839694656489</v>
+        <v>30.06535947712418</v>
       </c>
     </row>
     <row r="25">
@@ -805,14 +808,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Not so much</t>
+          <t>Not at all</t>
         </is>
       </c>
       <c r="C25">
-        <v>594</v>
+        <v>109</v>
       </c>
       <c r="D25">
-        <v>18.13740458015267</v>
+        <v>6.47653000594177</v>
       </c>
     </row>
     <row r="26">
@@ -823,38 +826,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Yes, completely</t>
+          <t>Don’t know</t>
         </is>
       </c>
       <c r="C26">
-        <v>447</v>
+        <v>233</v>
       </c>
       <c r="D26">
-        <v>13.64885496183206</v>
+        <v>13.84432560903149</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Responsiveness</t>
+          <t>Transparency</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Don’t know</t>
+          <t>Yes completely</t>
         </is>
       </c>
       <c r="C27">
-        <v>590</v>
+        <v>122</v>
       </c>
       <c r="D27">
-        <v>18.01526717557252</v>
+        <v>7.24896019013666</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Responsiveness</t>
+          <t>Transparency</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -863,154 +866,372 @@
         </is>
       </c>
       <c r="C28">
-        <v>1387</v>
+        <v>758</v>
       </c>
       <c r="D28">
-        <v>42.35114503816794</v>
+        <v>45.03862150920974</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Responsiveness</t>
+          <t>Transparency</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Not at all</t>
+          <t>Not so much</t>
         </is>
       </c>
       <c r="C29">
-        <v>179</v>
+        <v>428</v>
       </c>
       <c r="D29">
-        <v>5.465648854961832</v>
+        <v>25.43077837195484</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Responsiveness</t>
+          <t>Transparency</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Not so much</t>
+          <t>Not at all</t>
         </is>
       </c>
       <c r="C30">
-        <v>652</v>
+        <v>156</v>
       </c>
       <c r="D30">
-        <v>19.90839694656488</v>
+        <v>9.269162210338681</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Responsiveness</t>
+          <t>Transparency</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Yes, completely</t>
+          <t>Don’t know</t>
         </is>
       </c>
       <c r="C31">
-        <v>467</v>
+        <v>219</v>
       </c>
       <c r="D31">
-        <v>14.25954198473282</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Transparency</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Don’t know</t>
-        </is>
-      </c>
-      <c r="C32">
-        <v>768</v>
-      </c>
-      <c r="D32">
-        <v>23.45038167938931</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Transparency</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Mostly yes</t>
-        </is>
-      </c>
-      <c r="C33">
-        <v>1069</v>
-      </c>
-      <c r="D33">
-        <v>32.64122137404581</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Transparency</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Not at all</t>
-        </is>
-      </c>
-      <c r="C34">
-        <v>427</v>
-      </c>
-      <c r="D34">
-        <v>13.0381679389313</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Transparency</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Not so much</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>568</v>
-      </c>
-      <c r="D35">
-        <v>17.34351145038168</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Transparency</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Yes, completely</t>
-        </is>
-      </c>
-      <c r="C36">
-        <v>443</v>
-      </c>
-      <c r="D36">
-        <v>13.52671755725191</v>
+        <v>13.01247771836007</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Province</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total Respondents</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Percentage (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bagmati</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kathmandu</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>1051</v>
+      </c>
+      <c r="D2">
+        <v>65.90000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bagmati</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Lalitpur</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>307</v>
+      </c>
+      <c r="D3">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bagmati</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bhaktapur</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>238</v>
+      </c>
+      <c r="D4">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bagmati</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>1596</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Koshi Province</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Morang</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>952</v>
+      </c>
+      <c r="D6">
+        <v>56.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Koshi Province</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sunsari</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>731</v>
+      </c>
+      <c r="D7">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Koshi Province</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>1683</v>
+      </c>
+      <c r="D8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lumbini</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Banke</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>412</v>
+      </c>
+      <c r="D9">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Lumbini</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bardiya</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>319</v>
+      </c>
+      <c r="D10">
+        <v>43.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Lumbini</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>731</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sudur Paschim</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kailali</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>607</v>
+      </c>
+      <c r="D12">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sudur Paschim</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kanchanpur</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>341</v>
+      </c>
+      <c r="D13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sudur Paschim</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>948</v>
+      </c>
+      <c r="D14">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Total Respondents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Received early warnings from NS: Yes</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Once beneficiary: Yes</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>1969</v>
       </c>
     </row>
   </sheetData>
@@ -1053,14 +1274,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Don’t know</t>
+          <t>Yes completely</t>
         </is>
       </c>
       <c r="C2">
-        <v>415</v>
+        <v>97</v>
       </c>
       <c r="D2">
-        <v>12.67175572519084</v>
+        <v>5.763517528223411</v>
       </c>
     </row>
     <row r="3">
@@ -1075,10 +1296,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>1562</v>
+        <v>606</v>
       </c>
       <c r="D3">
-        <v>47.69465648854962</v>
+        <v>36.00713012477718</v>
       </c>
     </row>
     <row r="4">
@@ -1089,14 +1310,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Not at all</t>
+          <t>Not so much</t>
         </is>
       </c>
       <c r="C4">
-        <v>133</v>
+        <v>425</v>
       </c>
       <c r="D4">
-        <v>4.061068702290076</v>
+        <v>25.25252525252525</v>
       </c>
     </row>
     <row r="5">
@@ -1107,14 +1328,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Not so much</t>
+          <t>Not at all</t>
         </is>
       </c>
       <c r="C5">
-        <v>599</v>
+        <v>76</v>
       </c>
       <c r="D5">
-        <v>18.29007633587786</v>
+        <v>4.515745692216281</v>
       </c>
     </row>
     <row r="6">
@@ -1125,14 +1346,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Yes, completely</t>
+          <t>Don’t know</t>
         </is>
       </c>
       <c r="C6">
-        <v>566</v>
+        <v>479</v>
       </c>
       <c r="D6">
-        <v>17.2824427480916</v>
+        <v>28.46108140225787</v>
       </c>
     </row>
     <row r="7">
@@ -1143,14 +1364,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Don’t know</t>
+          <t>Yes completely</t>
         </is>
       </c>
       <c r="C7">
-        <v>617</v>
+        <v>114</v>
       </c>
       <c r="D7">
-        <v>18.83969465648855</v>
+        <v>6.773618538324421</v>
       </c>
     </row>
     <row r="8">
@@ -1165,10 +1386,10 @@
         </is>
       </c>
       <c r="C8">
-        <v>1469</v>
+        <v>746</v>
       </c>
       <c r="D8">
-        <v>44.85496183206107</v>
+        <v>44.32560903149139</v>
       </c>
     </row>
     <row r="9">
@@ -1179,14 +1400,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Not at all</t>
+          <t>Not so much</t>
         </is>
       </c>
       <c r="C9">
-        <v>139</v>
+        <v>435</v>
       </c>
       <c r="D9">
-        <v>4.244274809160306</v>
+        <v>25.84670231729055</v>
       </c>
     </row>
     <row r="10">
@@ -1197,14 +1418,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Not so much</t>
+          <t>Not at all</t>
         </is>
       </c>
       <c r="C10">
-        <v>541</v>
+        <v>124</v>
       </c>
       <c r="D10">
-        <v>16.51908396946565</v>
+        <v>7.36779560308972</v>
       </c>
     </row>
     <row r="11">
@@ -1215,14 +1436,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yes, completely</t>
+          <t>Don’t know</t>
         </is>
       </c>
       <c r="C11">
-        <v>509</v>
+        <v>264</v>
       </c>
       <c r="D11">
-        <v>15.54198473282443</v>
+        <v>15.68627450980392</v>
       </c>
     </row>
     <row r="12">
@@ -1233,14 +1454,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Don’t know</t>
+          <t>Yes completely</t>
         </is>
       </c>
       <c r="C12">
-        <v>375</v>
+        <v>186</v>
       </c>
       <c r="D12">
-        <v>11.45038167938931</v>
+        <v>11.05169340463458</v>
       </c>
     </row>
     <row r="13">
@@ -1255,10 +1476,10 @@
         </is>
       </c>
       <c r="C13">
-        <v>1503</v>
+        <v>938</v>
       </c>
       <c r="D13">
-        <v>45.89312977099237</v>
+        <v>55.73380867498514</v>
       </c>
     </row>
     <row r="14">
@@ -1269,14 +1490,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Not at all</t>
+          <t>Not so much</t>
         </is>
       </c>
       <c r="C14">
-        <v>200</v>
+        <v>337</v>
       </c>
       <c r="D14">
-        <v>6.106870229007633</v>
+        <v>20.02376708259061</v>
       </c>
     </row>
     <row r="15">
@@ -1287,14 +1508,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Not so much</t>
+          <t>Not at all</t>
         </is>
       </c>
       <c r="C15">
-        <v>558</v>
+        <v>76</v>
       </c>
       <c r="D15">
-        <v>17.0381679389313</v>
+        <v>4.515745692216281</v>
       </c>
     </row>
     <row r="16">
@@ -1305,38 +1526,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Yes, completely</t>
+          <t>Don’t know</t>
         </is>
       </c>
       <c r="C16">
-        <v>639</v>
+        <v>146</v>
       </c>
       <c r="D16">
-        <v>19.51145038167939</v>
+        <v>8.674985145573382</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Inclusiveness</t>
+          <t>Inclusiness</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Don’t know</t>
+          <t>Yes completely</t>
         </is>
       </c>
       <c r="C17">
-        <v>589</v>
+        <v>77</v>
       </c>
       <c r="D17">
-        <v>17.98473282442748</v>
+        <v>4.57516339869281</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Inclusiveness</t>
+          <t>Inclusiness</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1345,64 +1566,64 @@
         </is>
       </c>
       <c r="C18">
-        <v>1450</v>
+        <v>691</v>
       </c>
       <c r="D18">
-        <v>44.27480916030535</v>
+        <v>41.05763517528224</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Inclusiveness</t>
+          <t>Inclusiness</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Not at all</t>
+          <t>Not so much</t>
         </is>
       </c>
       <c r="C19">
-        <v>153</v>
+        <v>513</v>
       </c>
       <c r="D19">
-        <v>4.67175572519084</v>
+        <v>30.48128342245989</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Inclusiveness</t>
+          <t>Inclusiness</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Not so much</t>
+          <t>Not at all</t>
         </is>
       </c>
       <c r="C20">
-        <v>466</v>
+        <v>114</v>
       </c>
       <c r="D20">
-        <v>14.22900763358779</v>
+        <v>6.773618538324421</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Inclusiveness</t>
+          <t>Inclusiness</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Yes, completely</t>
+          <t>Don’t know</t>
         </is>
       </c>
       <c r="C21">
-        <v>617</v>
+        <v>288</v>
       </c>
       <c r="D21">
-        <v>18.83969465648855</v>
+        <v>17.11229946524064</v>
       </c>
     </row>
     <row r="22">
@@ -1413,14 +1634,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Don’t know</t>
+          <t>Yes completely</t>
         </is>
       </c>
       <c r="C22">
-        <v>632</v>
+        <v>92</v>
       </c>
       <c r="D22">
-        <v>19.29770992366412</v>
+        <v>5.466428995840761</v>
       </c>
     </row>
     <row r="23">
@@ -1435,10 +1656,10 @@
         </is>
       </c>
       <c r="C23">
-        <v>1361</v>
+        <v>716</v>
       </c>
       <c r="D23">
-        <v>41.55725190839695</v>
+        <v>42.54307783719548</v>
       </c>
     </row>
     <row r="24">
@@ -1449,14 +1670,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Not at all</t>
+          <t>Not so much</t>
         </is>
       </c>
       <c r="C24">
-        <v>184</v>
+        <v>501</v>
       </c>
       <c r="D24">
-        <v>5.618320610687022</v>
+        <v>29.76827094474153</v>
       </c>
     </row>
     <row r="25">
@@ -1467,14 +1688,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Not so much</t>
+          <t>Not at all</t>
         </is>
       </c>
       <c r="C25">
-        <v>628</v>
+        <v>96</v>
       </c>
       <c r="D25">
-        <v>19.17557251908397</v>
+        <v>5.704099821746881</v>
       </c>
     </row>
     <row r="26">
@@ -1485,14 +1706,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Yes, completely</t>
+          <t>Don’t know</t>
         </is>
       </c>
       <c r="C26">
-        <v>470</v>
+        <v>278</v>
       </c>
       <c r="D26">
-        <v>14.35114503816794</v>
+        <v>16.51812240047534</v>
       </c>
     </row>
     <row r="27">
@@ -1503,14 +1724,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Don’t know</t>
+          <t>Yes completely</t>
         </is>
       </c>
       <c r="C27">
-        <v>551</v>
+        <v>103</v>
       </c>
       <c r="D27">
-        <v>16.82442748091603</v>
+        <v>6.120023767082591</v>
       </c>
     </row>
     <row r="28">
@@ -1525,10 +1746,10 @@
         </is>
       </c>
       <c r="C28">
-        <v>1334</v>
+        <v>758</v>
       </c>
       <c r="D28">
-        <v>40.73282442748092</v>
+        <v>45.03862150920974</v>
       </c>
     </row>
     <row r="29">
@@ -1539,14 +1760,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Not at all</t>
+          <t>Not so much</t>
         </is>
       </c>
       <c r="C29">
-        <v>146</v>
+        <v>419</v>
       </c>
       <c r="D29">
-        <v>4.458015267175573</v>
+        <v>24.89601901366607</v>
       </c>
     </row>
     <row r="30">
@@ -1557,14 +1778,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Not so much</t>
+          <t>Not at all</t>
         </is>
       </c>
       <c r="C30">
-        <v>740</v>
+        <v>120</v>
       </c>
       <c r="D30">
-        <v>22.59541984732824</v>
+        <v>7.130124777183601</v>
       </c>
     </row>
     <row r="31">
@@ -1575,14 +1796,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Yes, completely</t>
+          <t>Don’t know</t>
         </is>
       </c>
       <c r="C31">
-        <v>504</v>
+        <v>283</v>
       </c>
       <c r="D31">
-        <v>15.38931297709924</v>
+        <v>16.81521093285799</v>
       </c>
     </row>
     <row r="32">
@@ -1593,14 +1814,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Don’t know</t>
+          <t>Yes completely</t>
         </is>
       </c>
       <c r="C32">
-        <v>851</v>
+        <v>103</v>
       </c>
       <c r="D32">
-        <v>25.98473282442748</v>
+        <v>6.120023767082591</v>
       </c>
     </row>
     <row r="33">
@@ -1615,10 +1836,10 @@
         </is>
       </c>
       <c r="C33">
-        <v>1064</v>
+        <v>773</v>
       </c>
       <c r="D33">
-        <v>32.48854961832061</v>
+        <v>45.92988710635769</v>
       </c>
     </row>
     <row r="34">
@@ -1629,14 +1850,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Not at all</t>
+          <t>Not so much</t>
         </is>
       </c>
       <c r="C34">
-        <v>348</v>
+        <v>413</v>
       </c>
       <c r="D34">
-        <v>10.62595419847328</v>
+        <v>24.53951277480689</v>
       </c>
     </row>
     <row r="35">
@@ -1647,14 +1868,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Not so much</t>
+          <t>Not at all</t>
         </is>
       </c>
       <c r="C35">
-        <v>494</v>
+        <v>140</v>
       </c>
       <c r="D35">
-        <v>15.08396946564886</v>
+        <v>8.318478906714201</v>
       </c>
     </row>
     <row r="36">
@@ -1665,14 +1886,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Yes, completely</t>
+          <t>Don’t know</t>
         </is>
       </c>
       <c r="C36">
-        <v>518</v>
+        <v>254</v>
       </c>
       <c r="D36">
-        <v>15.81679389312977</v>
+        <v>15.09209744503862</v>
       </c>
     </row>
   </sheetData>
@@ -1682,7 +1903,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1710,244 +1931,631 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Did you personally
-receive any other
-warnings?</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes completely</t>
         </is>
       </c>
       <c r="C2">
-        <v>1120</v>
+        <v>644</v>
       </c>
       <c r="D2">
-        <v>34.19847328244275</v>
+        <v>12.98910851149657</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Did you personally
-receive any other
-warnings?</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>No answer</t>
+          <t>Mostly yes</t>
         </is>
       </c>
       <c r="C3">
-        <v>298</v>
+        <v>1857</v>
       </c>
       <c r="D3">
-        <v>9.099236641221374</v>
+        <v>37.45461879790238</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Did you personally
-receive any other
-warnings?</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not so much</t>
         </is>
       </c>
       <c r="C4">
-        <v>1857</v>
+        <v>1183</v>
       </c>
       <c r="D4">
-        <v>56.70229007633588</v>
+        <v>23.86042759177088</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Did you personally
-receive the
-warning(s) by Nepal
-Red Cross?</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not at all</t>
         </is>
       </c>
       <c r="C5">
-        <v>1437</v>
+        <v>344</v>
       </c>
       <c r="D5">
-        <v>43.87786259541985</v>
+        <v>6.938281565147236</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Did you personally
-receive the
-warning(s) by Nepal
-Red Cross?</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>No answer</t>
+          <t>Don’t know</t>
         </is>
       </c>
       <c r="C6">
-        <v>338</v>
+        <v>930</v>
       </c>
       <c r="D6">
-        <v>10.3206106870229</v>
+        <v>18.75756353368294</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Did you personally
-receive the
-warning(s) by Nepal
-Red Cross?</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes completely</t>
         </is>
       </c>
       <c r="C7">
-        <v>1500</v>
+        <v>947</v>
       </c>
       <c r="D7">
-        <v>45.80152671755725</v>
+        <v>19.1004437273094</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Have been ever
-received aid or
-support</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Mostly yes</t>
         </is>
       </c>
       <c r="C8">
-        <v>1874</v>
+        <v>2211</v>
       </c>
       <c r="D8">
-        <v>57.22137404580153</v>
+        <v>44.5945945945946</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Have been ever
-received aid or
-support</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not so much</t>
         </is>
       </c>
       <c r="C9">
-        <v>1401</v>
+        <v>792</v>
       </c>
       <c r="D9">
-        <v>42.77862595419847</v>
+        <v>15.97418313836224</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Have you ever
-volunteered at Nepal
-Red Cross Society?</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not at all</t>
         </is>
       </c>
       <c r="C10">
-        <v>2780</v>
+        <v>209</v>
       </c>
       <c r="D10">
-        <v>84.88549618320612</v>
+        <v>4.215409439290037</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Have you ever
-volunteered at Nepal
-Red Cross Society?</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Don’t know</t>
         </is>
       </c>
       <c r="C11">
-        <v>495</v>
+        <v>799</v>
       </c>
       <c r="D11">
-        <v>15.11450381679389</v>
+        <v>16.11536910044373</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Have you ever made
-a donation to Nepal
-Red Cross Society?</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes completely</t>
         </is>
       </c>
       <c r="C12">
-        <v>2492</v>
+        <v>808</v>
       </c>
       <c r="D12">
-        <v>76.09160305343512</v>
+        <v>16.29689390883421</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Have you ever made
-a donation to Nepal
-Red Cross Society?</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Mostly yes</t>
         </is>
       </c>
       <c r="C13">
-        <v>783</v>
+        <v>2260</v>
       </c>
       <c r="D13">
-        <v>23.90839694656488</v>
+        <v>45.58289632916498</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Not so much</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>875</v>
+      </c>
+      <c r="D14">
+        <v>17.64824526018556</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Not at all</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>297</v>
+      </c>
+      <c r="D15">
+        <v>5.990318676885841</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Don’t know</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>718</v>
+      </c>
+      <c r="D16">
+        <v>14.48164582492941</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Inclusiness</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Yes completely</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>892</v>
+      </c>
+      <c r="D17">
+        <v>17.99112545381202</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Inclusiness</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Mostly yes</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>1841</v>
+      </c>
+      <c r="D18">
+        <v>37.13190802743041</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Inclusiness</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Not so much</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>972</v>
+      </c>
+      <c r="D19">
+        <v>19.60467930617184</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Inclusiness</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Not at all</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>324</v>
+      </c>
+      <c r="D20">
+        <v>6.53489310205728</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Inclusiness</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Don’t know</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>929</v>
+      </c>
+      <c r="D21">
+        <v>18.73739411052844</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Participation</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Yes completely</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>532</v>
+      </c>
+      <c r="D22">
+        <v>10.73013311819282</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Participation</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mostly yes</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>1588</v>
+      </c>
+      <c r="D23">
+        <v>32.02904396934247</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Participation</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Not so much</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>1003</v>
+      </c>
+      <c r="D24">
+        <v>20.22993142396128</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Participation</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Not at all</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>503</v>
+      </c>
+      <c r="D25">
+        <v>10.14521984671238</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Participation</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Don’t know</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>1332</v>
+      </c>
+      <c r="D26">
+        <v>26.86567164179105</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Responsiveness</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Yes completely</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>573</v>
+      </c>
+      <c r="D27">
+        <v>11.55707946752723</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Responsiveness</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mostly yes</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>2099</v>
+      </c>
+      <c r="D28">
+        <v>42.33561920129084</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Responsiveness</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Not so much</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>1090</v>
+      </c>
+      <c r="D29">
+        <v>21.98467123840258</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Responsiveness</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Not at all</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>315</v>
+      </c>
+      <c r="D30">
+        <v>6.353368293666802</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Responsiveness</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Don’t know</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>881</v>
+      </c>
+      <c r="D31">
+        <v>17.76926179911255</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Transparency</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Yes completely</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>534</v>
+      </c>
+      <c r="D32">
+        <v>10.77047196450182</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Transparency</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Mostly yes</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>1666</v>
+      </c>
+      <c r="D33">
+        <v>33.6022589753933</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Transparency</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Not so much</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>938</v>
+      </c>
+      <c r="D34">
+        <v>18.91891891891892</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Transparency</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Not at all</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>645</v>
+      </c>
+      <c r="D35">
+        <v>13.00927793465107</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Transparency</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Don’t know</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>1175</v>
+      </c>
+      <c r="D36">
+        <v>23.69907220653489</v>
       </c>
     </row>
   </sheetData>
@@ -1957,38 +2565,28 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Drivers</t>
+          <t>Question</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Dimension</t>
+          <t>Response</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Beneficiaries</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Volunteers</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Others</t>
+          <t>percent</t>
         </is>
       </c>
     </row>
@@ -2000,188 +2598,140 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Yes completely</t>
         </is>
       </c>
       <c r="C2">
-        <v>6.372023367182443</v>
+        <v>685</v>
       </c>
       <c r="D2">
-        <v>6.957053735051803</v>
-      </c>
-      <c r="E2">
-        <v>7.594520962860048</v>
-      </c>
-      <c r="F2">
-        <v>5.770827207196321</v>
+        <v>13.81605486083098</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Effectiveness</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Mostly yes</t>
         </is>
       </c>
       <c r="C3">
-        <v>5.953070734590336</v>
+        <v>2466</v>
       </c>
       <c r="D3">
-        <v>6.703194780367792</v>
-      </c>
-      <c r="E3">
-        <v>6.961315132071824</v>
-      </c>
-      <c r="F3">
-        <v>5.246273156228286</v>
+        <v>49.73779749899153</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Not so much</t>
         </is>
       </c>
       <c r="C4">
-        <v>6.494071908698798</v>
+        <v>990</v>
       </c>
       <c r="D4">
-        <v>6.784371808483366</v>
-      </c>
-      <c r="E4">
-        <v>7.372679264750475</v>
-      </c>
-      <c r="F4">
-        <v>6.143904960290916</v>
+        <v>19.9677289229528</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Inclusiveness</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Not at all</t>
         </is>
       </c>
       <c r="C5">
-        <v>6.150307275201435</v>
+        <v>203</v>
       </c>
       <c r="D5">
-        <v>6.842585168743797</v>
-      </c>
-      <c r="E5">
-        <v>7.157859894799513</v>
-      </c>
-      <c r="F5">
-        <v>5.479821435411362</v>
+        <v>4.09439290036305</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Participation</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Don’t know</t>
         </is>
       </c>
       <c r="C6">
-        <v>5.778633109295288</v>
+        <v>614</v>
       </c>
       <c r="D6">
-        <v>6.600704971572226</v>
-      </c>
-      <c r="E6">
-        <v>6.921698605372656</v>
-      </c>
-      <c r="F6">
-        <v>5.008540842889779</v>
+        <v>12.38402581686164</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Responsiveness</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Yes completely</t>
         </is>
       </c>
       <c r="C7">
-        <v>5.942776864916419</v>
+        <v>586</v>
       </c>
       <c r="D7">
-        <v>6.672693211255257</v>
-      </c>
-      <c r="E7">
-        <v>7.049431608801407</v>
-      </c>
-      <c r="F7">
-        <v>5.239467264782529</v>
+        <v>11.8192819685357</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Transparency</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Mostly yes</t>
         </is>
       </c>
       <c r="C8">
-        <v>5.131771433639727</v>
+        <v>2107</v>
       </c>
       <c r="D8">
-        <v>5.959981263906206</v>
-      </c>
-      <c r="E8">
-        <v>6.426130252364075</v>
-      </c>
-      <c r="F8">
-        <v>4.372283426523087</v>
+        <v>42.49697458652683</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dissemination</t>
+          <t>Not so much</t>
         </is>
       </c>
       <c r="C9">
-        <v>5.762231190952609</v>
+        <v>1026</v>
       </c>
       <c r="D9">
-        <v>6.584369082057098</v>
-      </c>
-      <c r="E9">
-        <v>6.807863488053773</v>
-      </c>
-      <c r="F9">
-        <v>5.024570235293842</v>
+        <v>20.69382815651472</v>
       </c>
     </row>
     <row r="10">
@@ -2192,212 +2742,482 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dissemination</t>
+          <t>Not at all</t>
         </is>
       </c>
       <c r="C10">
-        <v>6.731507349688885</v>
+        <v>277</v>
       </c>
       <c r="D10">
-        <v>7.340652564272804</v>
-      </c>
-      <c r="E10">
-        <v>7.647766000297698</v>
-      </c>
-      <c r="F10">
-        <v>6.142954537149642</v>
+        <v>5.586930213795886</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Effectiveness</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dissemination</t>
+          <t>Don’t know</t>
         </is>
       </c>
       <c r="C11">
-        <v>6.233280102512579</v>
+        <v>962</v>
       </c>
       <c r="D11">
-        <v>6.64598752382052</v>
-      </c>
-      <c r="E11">
-        <v>7.382990223910638</v>
-      </c>
-      <c r="F11">
-        <v>5.768503239188466</v>
+        <v>19.40298507462687</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Inclusiveness</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dissemination</t>
+          <t>Yes completely</t>
         </is>
       </c>
       <c r="C12">
-        <v>6.4638361742105</v>
+        <v>813</v>
       </c>
       <c r="D12">
-        <v>7.085319814279025</v>
-      </c>
-      <c r="E12">
-        <v>7.457171231390435</v>
-      </c>
-      <c r="F12">
-        <v>5.885679222831259</v>
+        <v>16.3977410246067</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Participation</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dissemination</t>
+          <t>Mostly yes</t>
         </is>
       </c>
       <c r="C13">
-        <v>4.855842204968685</v>
+        <v>2379</v>
       </c>
       <c r="D13">
-        <v>5.714729046996554</v>
-      </c>
-      <c r="E13">
-        <v>6.480631870329334</v>
-      </c>
-      <c r="F13">
-        <v>4.035710647626185</v>
+        <v>47.98305768455023</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Responsiveness</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dissemination</t>
+          <t>Not so much</t>
         </is>
       </c>
       <c r="C14">
-        <v>5.804334508190558</v>
+        <v>915</v>
       </c>
       <c r="D14">
-        <v>6.537721630749502</v>
-      </c>
-      <c r="E14">
-        <v>7.087034075975749</v>
-      </c>
-      <c r="F14">
-        <v>5.087978216497428</v>
+        <v>18.45502218636547</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Transparency</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dissemination</t>
+          <t>Not at all</t>
         </is>
       </c>
       <c r="C15">
-        <v>5.103778001159593</v>
+        <v>291</v>
       </c>
       <c r="D15">
-        <v>5.944701127086958</v>
-      </c>
-      <c r="E15">
-        <v>6.780650130443699</v>
-      </c>
-      <c r="F15">
-        <v>4.272984816271666</v>
+        <v>5.869302137958854</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dissemination</t>
+          <t>Don’t know</t>
         </is>
       </c>
       <c r="C16">
-        <v>5.850687075954773</v>
+        <v>560</v>
       </c>
       <c r="D16">
-        <v>6.550497255608923</v>
-      </c>
-      <c r="E16">
-        <v>7.092015288628761</v>
-      </c>
-      <c r="F16">
-        <v>5.174054416408355</v>
+        <v>11.29487696651876</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Inclusiness</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Yes completely</t>
         </is>
       </c>
       <c r="C17">
-        <v>5.974664956217778</v>
+        <v>683</v>
       </c>
       <c r="D17">
-        <v>6.645797848482921</v>
-      </c>
-      <c r="E17">
-        <v>7.06909081728857</v>
-      </c>
-      <c r="F17">
-        <v>5.32301689904604</v>
+        <v>13.77571601452198</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Inclusiness</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EWS INDEX</t>
+          <t>Mostly yes</t>
         </is>
       </c>
       <c r="C18">
-        <v>5.912676016086275</v>
+        <v>2071</v>
       </c>
       <c r="D18">
-        <v>6.598147552045923</v>
-      </c>
-      <c r="E18">
-        <v>7.080553052958665</v>
-      </c>
-      <c r="F18">
-        <v>5.248535657727198</v>
+        <v>41.7708753529649</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Inclusiness</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Not so much</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>909</v>
+      </c>
+      <c r="D19">
+        <v>18.33400564743848</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Inclusiness</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Not at all</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>292</v>
+      </c>
+      <c r="D20">
+        <v>5.889471561113352</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Inclusiness</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Don’t know</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>1003</v>
+      </c>
+      <c r="D21">
+        <v>20.22993142396128</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Participation</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Yes completely</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>573</v>
+      </c>
+      <c r="D22">
+        <v>11.55707946752723</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Participation</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mostly yes</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>2016</v>
+      </c>
+      <c r="D23">
+        <v>40.66155707946753</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Participation</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Not so much</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>1145</v>
+      </c>
+      <c r="D24">
+        <v>23.09398951189996</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Participation</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Not at all</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>302</v>
+      </c>
+      <c r="D25">
+        <v>6.091165792658329</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Participation</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Don’t know</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>922</v>
+      </c>
+      <c r="D26">
+        <v>18.59620814844696</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Responsiveness</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Yes completely</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>571</v>
+      </c>
+      <c r="D27">
+        <v>11.51674062121823</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Responsiveness</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mostly yes</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>2027</v>
+      </c>
+      <c r="D28">
+        <v>40.883420734167</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Responsiveness</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Not so much</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>1280</v>
+      </c>
+      <c r="D29">
+        <v>25.81686163775716</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Responsiveness</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Not at all</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>233</v>
+      </c>
+      <c r="D30">
+        <v>4.699475594997983</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Responsiveness</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Don’t know</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>847</v>
+      </c>
+      <c r="D31">
+        <v>17.08350141185962</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Transparency</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Yes completely</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>599</v>
+      </c>
+      <c r="D32">
+        <v>12.08148446954417</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Transparency</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Mostly yes</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>1675</v>
+      </c>
+      <c r="D33">
+        <v>33.78378378378378</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Transparency</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Not so much</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>872</v>
+      </c>
+      <c r="D34">
+        <v>17.58773699072207</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Transparency</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Not at all</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>518</v>
+      </c>
+      <c r="D35">
+        <v>10.44776119402985</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Transparency</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Don’t know</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>1294</v>
+      </c>
+      <c r="D36">
+        <v>26.09923356192013</v>
       </c>
     </row>
   </sheetData>
@@ -2407,63 +3227,182 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Age Group</t>
+          <t>Question</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Total Respondents</t>
+          <t>Response</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Percentage (%)</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>percent</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18-39</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>1780</v>
+          <t>Did you personally
+receive any other
+warnings?</t>
+        </is>
       </c>
       <c r="C2">
-        <v>54.4</v>
+        <v>604</v>
+      </c>
+      <c r="D2">
+        <v>12.18233158531666</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>40-59</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>938</v>
+          <t>Did you personally
+receive any other
+warnings?</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C3">
-        <v>28.6</v>
+        <v>1560</v>
+      </c>
+      <c r="D3">
+        <v>31.46430012101654</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>60+</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>557</v>
+          <t>Did you personally
+receive any other
+warnings?</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="C4">
-        <v>17</v>
+        <v>2794</v>
+      </c>
+      <c r="D4">
+        <v>56.3533682936668</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Did you personally
+receive the
+warning(s) by Nepal
+Red Cross?</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>660</v>
+      </c>
+      <c r="D5">
+        <v>13.31181928196853</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Did you personally
+receive the
+warning(s) by Nepal
+Red Cross?</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>2327</v>
+      </c>
+      <c r="D6">
+        <v>46.93424768051634</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Did you personally
+receive the
+warning(s) by Nepal
+Red Cross?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>1971</v>
+      </c>
+      <c r="D7">
+        <v>39.75393303751513</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Have been ever
+received aid or
+support</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>2989</v>
+      </c>
+      <c r="D8">
+        <v>60.28640580879387</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Have been ever
+received aid or
+support</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>1969</v>
+      </c>
+      <c r="D9">
+        <v>39.71359419120613</v>
       </c>
     </row>
   </sheetData>
@@ -2473,76 +3412,874 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Dimension</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Total Respondents</t>
+          <t>Drivers</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Percentage (%)</t>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Received early warnings from NS: Yes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Once beneficiary: Yes</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Others</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>1643</v>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
       </c>
       <c r="C2">
-        <v>50.2</v>
+        <v>6.140691194032051</v>
+      </c>
+      <c r="D2">
+        <v>6.935817744170905</v>
+      </c>
+      <c r="E2">
+        <v>6.540771556105287</v>
+      </c>
+      <c r="F2">
+        <v>5.440492725310862</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>1632</v>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
       </c>
       <c r="C3">
-        <v>49.8</v>
+        <v>5.969378157556003</v>
+      </c>
+      <c r="D3">
+        <v>6.956057756593789</v>
+      </c>
+      <c r="E3">
+        <v>6.511307386960535</v>
+      </c>
+      <c r="F3">
+        <v>5.026617149052426</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Other or did not answer</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>0</v>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>6.180207835840202</v>
+      </c>
+      <c r="D4">
+        <v>6.926395233215744</v>
+      </c>
+      <c r="E4">
+        <v>6.504927346330206</v>
+      </c>
+      <c r="F4">
+        <v>5.574736440790631</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>3275</v>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Inclusiness</t>
+        </is>
       </c>
       <c r="C5">
-        <v>100</v>
+        <v>6.147678176080349</v>
+      </c>
+      <c r="D5">
+        <v>7.090835467957054</v>
+      </c>
+      <c r="E5">
+        <v>6.610257692506353</v>
+      </c>
+      <c r="F5">
+        <v>5.203768286354878</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Participation</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>5.736293787273688</v>
+      </c>
+      <c r="D6">
+        <v>6.780070919880633</v>
+      </c>
+      <c r="E6">
+        <v>6.350747622807971</v>
+      </c>
+      <c r="F6">
+        <v>4.760369353816578</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Responsiveness</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>5.738617790816408</v>
+      </c>
+      <c r="D7">
+        <v>6.5857147172774</v>
+      </c>
+      <c r="E7">
+        <v>6.220988738815316</v>
+      </c>
+      <c r="F7">
+        <v>4.949404658264032</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Transparency</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>5.499084342943783</v>
+      </c>
+      <c r="D8">
+        <v>6.495055116437627</v>
+      </c>
+      <c r="E8">
+        <v>6.108562177009405</v>
+      </c>
+      <c r="F8">
+        <v>4.444768791335812</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Detection</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>5.298441356508704</v>
+      </c>
+      <c r="D9">
+        <v>6.699340674360259</v>
+      </c>
+      <c r="E9">
+        <v>6.125091252255332</v>
+      </c>
+      <c r="F9">
+        <v>4.457824647460592</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Detection</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>5.360006442773939</v>
+      </c>
+      <c r="D10">
+        <v>6.517391060804297</v>
+      </c>
+      <c r="E10">
+        <v>5.883176634864193</v>
+      </c>
+      <c r="F10">
+        <v>4.828845818177468</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Detection</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>5.979057147138445</v>
+      </c>
+      <c r="D11">
+        <v>6.81911653780342</v>
+      </c>
+      <c r="E11">
+        <v>6.243378152677427</v>
+      </c>
+      <c r="F11">
+        <v>5.688569481220322</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Detection</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Inclusiness</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>5.040745419283344</v>
+      </c>
+      <c r="D12">
+        <v>6.219461975172204</v>
+      </c>
+      <c r="E12">
+        <v>5.752029284396507</v>
+      </c>
+      <c r="F12">
+        <v>4.440611188876832</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Detection</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Participation</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>5.166518856823748</v>
+      </c>
+      <c r="D13">
+        <v>6.064375744102009</v>
+      </c>
+      <c r="E13">
+        <v>5.89154722802086</v>
+      </c>
+      <c r="F13">
+        <v>4.660583782470507</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Detection</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Responsiveness</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>5.364749204027447</v>
+      </c>
+      <c r="D14">
+        <v>6.406276735163227</v>
+      </c>
+      <c r="E14">
+        <v>6.059068824533655</v>
+      </c>
+      <c r="F14">
+        <v>4.784355495296563</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Detection</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Transparency</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>5.242403386911856</v>
+      </c>
+      <c r="D15">
+        <v>6.333979385798642</v>
+      </c>
+      <c r="E15">
+        <v>5.894560129729904</v>
+      </c>
+      <c r="F15">
+        <v>4.732096574978481</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Disaster</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>5.494079251828212</v>
+      </c>
+      <c r="D16">
+        <v>6.587033534983388</v>
+      </c>
+      <c r="E16">
+        <v>6.058127664374444</v>
+      </c>
+      <c r="F16">
+        <v>4.996976897612208</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Disaster</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>5.643836466568732</v>
+      </c>
+      <c r="D17">
+        <v>6.541070254877365</v>
+      </c>
+      <c r="E17">
+        <v>6.130142828317173</v>
+      </c>
+      <c r="F17">
+        <v>5.241240265362951</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Disaster</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>6.01022081130316</v>
+      </c>
+      <c r="D18">
+        <v>6.884789544635225</v>
+      </c>
+      <c r="E18">
+        <v>6.3154090119092</v>
+      </c>
+      <c r="F18">
+        <v>5.70321895367784</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Disaster</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Inclusiness</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>5.405546376058279</v>
+      </c>
+      <c r="D19">
+        <v>6.494210433413884</v>
+      </c>
+      <c r="E19">
+        <v>6.035340190709184</v>
+      </c>
+      <c r="F19">
+        <v>4.891296045001209</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Disaster</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Participation</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>5.132347043542019</v>
+      </c>
+      <c r="D20">
+        <v>6.251964488462063</v>
+      </c>
+      <c r="E20">
+        <v>5.922484961844537</v>
+      </c>
+      <c r="F20">
+        <v>4.526327861452295</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Disaster</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Transparency</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>5.169899927545419</v>
+      </c>
+      <c r="D21">
+        <v>6.651142724091334</v>
+      </c>
+      <c r="E21">
+        <v>6.021485984710894</v>
+      </c>
+      <c r="F21">
+        <v>4.452489891235014</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Dissemination</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>5.653873738675299</v>
+      </c>
+      <c r="D22">
+        <v>6.913958770822318</v>
+      </c>
+      <c r="E22">
+        <v>6.274442415807243</v>
+      </c>
+      <c r="F22">
+        <v>4.447318515288933</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Dissemination</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>6.608670871306107</v>
+      </c>
+      <c r="D23">
+        <v>7.500933956671988</v>
+      </c>
+      <c r="E23">
+        <v>7.012129867345133</v>
+      </c>
+      <c r="F23">
+        <v>5.758018334660184</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Dissemination</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>6.178025995654862</v>
+      </c>
+      <c r="D24">
+        <v>7.041931587911988</v>
+      </c>
+      <c r="E24">
+        <v>6.516116824320966</v>
+      </c>
+      <c r="F24">
+        <v>5.496502052247435</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Dissemination</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Inclusiness</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>6.255146619568079</v>
+      </c>
+      <c r="D25">
+        <v>7.327812013364759</v>
+      </c>
+      <c r="E25">
+        <v>6.748165302715698</v>
+      </c>
+      <c r="F25">
+        <v>5.245683094552268</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Dissemination</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Participation</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>5.363703706241167</v>
+      </c>
+      <c r="D26">
+        <v>6.361270789935952</v>
+      </c>
+      <c r="E26">
+        <v>5.98526656320569</v>
+      </c>
+      <c r="F26">
+        <v>4.271741008032007</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Dissemination</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Responsiveness</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>5.807173588232851</v>
+      </c>
+      <c r="D27">
+        <v>6.814668258728242</v>
+      </c>
+      <c r="E27">
+        <v>6.262129315084895</v>
+      </c>
+      <c r="F27">
+        <v>4.852168177830872</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dissemination</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Transparency</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>5.13764258833648</v>
+      </c>
+      <c r="D28">
+        <v>6.432137057826754</v>
+      </c>
+      <c r="E28">
+        <v>5.967945210341517</v>
+      </c>
+      <c r="F28">
+        <v>3.747190939158246</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Detection</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>5.350274544781069</v>
+      </c>
+      <c r="D29">
+        <v>6.43713458760058</v>
+      </c>
+      <c r="E29">
+        <v>5.978407358068268</v>
+      </c>
+      <c r="F29">
+        <v>4.798983855497252</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Disaster</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>5.475988312807637</v>
+      </c>
+      <c r="D30">
+        <v>6.568368496743877</v>
+      </c>
+      <c r="E30">
+        <v>6.080498440310905</v>
+      </c>
+      <c r="F30">
+        <v>4.968591652390253</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Dissemination</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>5.857748158287835</v>
+      </c>
+      <c r="D31">
+        <v>6.913244633608858</v>
+      </c>
+      <c r="E31">
+        <v>6.395170785545877</v>
+      </c>
+      <c r="F31">
+        <v>4.83123173168142</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>5.915993040648926</v>
+      </c>
+      <c r="D32">
+        <v>6.824278136504736</v>
+      </c>
+      <c r="E32">
+        <v>6.406794645790725</v>
+      </c>
+      <c r="F32">
+        <v>5.057165343560746</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Competency</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>5.8164922945805</v>
+      </c>
+      <c r="D33">
+        <v>6.795794766983906</v>
+      </c>
+      <c r="E33">
+        <v>6.302371048698685</v>
+      </c>
+      <c r="F33">
+        <v>5.131766607669821</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>5.30598670495227</v>
+      </c>
+      <c r="D34">
+        <v>6.421249528316877</v>
+      </c>
+      <c r="E34">
+        <v>6.017824984708847</v>
+      </c>
+      <c r="F34">
+        <v>4.449446025309867</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>5.712279147747513</v>
+      </c>
+      <c r="D35">
+        <v>6.783079972476975</v>
+      </c>
+      <c r="E35">
+        <v>6.286448117581935</v>
+      </c>
+      <c r="F35">
+        <v>4.945339653696297</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>EWS INDEX</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>5.650001014131367</v>
+      </c>
+      <c r="D36">
+        <v>6.685756463614513</v>
+      </c>
+      <c r="E36">
+        <v>6.215217807428944</v>
+      </c>
+      <c r="F36">
+        <v>4.913993145782418</v>
       </c>
     </row>
   </sheetData>
@@ -2552,209 +4289,4367 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:F153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Region</t>
+          <t>variable</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>District</t>
+          <t>variable_value</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Total Respondents</t>
+          <t>dimension</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Percentage (%)</t>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>long_label</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bagmati</t>
+          <t>Provinces</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kathmandu</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>1051</v>
+          <t>Koshi Province</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
       </c>
       <c r="D2">
-        <v>65.90000000000001</v>
+        <v>5.460474037539389</v>
+      </c>
+      <c r="E2">
+        <v>1683</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Provinces</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bagmati</t>
+          <t>Provinces</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lalitpur</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>307</v>
+          <t>Koshi Province</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
       </c>
       <c r="D3">
-        <v>19.2</v>
+        <v>5.275296684901204</v>
+      </c>
+      <c r="E3">
+        <v>1683</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Provinces</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Provinces</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Bagmati</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bhaktapur</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>238</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
       </c>
       <c r="D4">
-        <v>14.9</v>
+        <v>5.307917797112296</v>
+      </c>
+      <c r="E4">
+        <v>1596</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Provinces</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bagmati</t>
+          <t>Provinces</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>1596</v>
+          <t>Koshi Province</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
       </c>
       <c r="D5">
-        <v>100</v>
+        <v>5.034977180015348</v>
+      </c>
+      <c r="E5">
+        <v>1683</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Provinces</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Provinces</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Lumbini</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Banke</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>412</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
       </c>
       <c r="D6">
-        <v>56.4</v>
+        <v>6.836163063182561</v>
+      </c>
+      <c r="E6">
+        <v>731</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Provinces</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lumbini</t>
+          <t>Provinces</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bardiya</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>319</v>
+          <t>Sudur Paschim</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
       </c>
       <c r="D7">
-        <v>43.6</v>
+        <v>6.219240737917366</v>
+      </c>
+      <c r="E7">
+        <v>948</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Provinces</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lumbini</t>
+          <t>Provinces</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>731</v>
+          <t>Bagmati</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
       </c>
       <c r="D8">
-        <v>100</v>
+        <v>5.488718524058838</v>
+      </c>
+      <c r="E8">
+        <v>1596</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Provinces</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sudur Paschim</t>
+          <t>Provinces</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kailali</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>607</v>
+          <t>Koshi Province</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
       </c>
       <c r="D9">
-        <v>64</v>
+        <v>5.120423546302943</v>
+      </c>
+      <c r="E9">
+        <v>1683</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Provinces</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sudur Paschim</t>
+          <t>Provinces</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kanchanpur</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>341</v>
+          <t>Lumbini</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
       </c>
       <c r="D10">
-        <v>36</v>
+        <v>6.829270992450908</v>
+      </c>
+      <c r="E10">
+        <v>731</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Provinces</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Provinces</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Sudur Paschim</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>6.144437573009001</v>
+      </c>
+      <c r="E11">
         <v>948</v>
       </c>
-      <c r="D11">
-        <v>100</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Provinces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Morang</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>5.156061701614846</v>
+      </c>
+      <c r="E12">
+        <v>952</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sunsari</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>5.861428571428571</v>
+      </c>
+      <c r="E13">
+        <v>731</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Morang</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>4.788542439990101</v>
+      </c>
+      <c r="E14">
+        <v>952</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sunsari</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>5.90422519127555</v>
+      </c>
+      <c r="E15">
+        <v>731</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Banke</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>7.291459369817579</v>
+      </c>
+      <c r="E16">
+        <v>412</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bardiya</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>6.256957002210166</v>
+      </c>
+      <c r="E17">
+        <v>319</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bhaktapur</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>6.598872882486328</v>
+      </c>
+      <c r="E18">
+        <v>238</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kailali</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>6.527308982383857</v>
+      </c>
+      <c r="E19">
+        <v>607</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kanchanpur</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>5.668202003023431</v>
+      </c>
+      <c r="E20">
+        <v>341</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kathmandu</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>4.900482258631151</v>
+      </c>
+      <c r="E21">
+        <v>1051</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Lalitpur</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>5.639252085014797</v>
+      </c>
+      <c r="E22">
+        <v>307</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Morang</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>4.472104442994854</v>
+      </c>
+      <c r="E23">
+        <v>952</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sunsari</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>5.743420452472177</v>
+      </c>
+      <c r="E24">
+        <v>731</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Banke</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>7.304650515176831</v>
+      </c>
+      <c r="E25">
+        <v>412</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bardiya</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>6.232804232804233</v>
+      </c>
+      <c r="E26">
+        <v>319</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Bhaktapur</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>6.520841670001333</v>
+      </c>
+      <c r="E27">
+        <v>238</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kailali</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>6.483873974645786</v>
+      </c>
+      <c r="E28">
+        <v>607</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kanchanpur</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>5.527656794425087</v>
+      </c>
+      <c r="E29">
+        <v>341</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kathmandu</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>5.165454255404004</v>
+      </c>
+      <c r="E30">
+        <v>1051</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Lalitpur</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>5.746354587032553</v>
+      </c>
+      <c r="E31">
+        <v>307</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Morang</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>4.678730158730159</v>
+      </c>
+      <c r="E32">
+        <v>952</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sunsari</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>5.694880264244426</v>
+      </c>
+      <c r="E33">
+        <v>731</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bhojpuri</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>4.598039215686274</v>
+      </c>
+      <c r="E34">
+        <v>39</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Maithili</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>5.071253372577876</v>
+      </c>
+      <c r="E35">
+        <v>493</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Nepali</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>5.674110384894698</v>
+      </c>
+      <c r="E36">
+        <v>2715</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Newari</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>5.277777777777778</v>
+      </c>
+      <c r="E37">
+        <v>357</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D38">
+        <v>5.252572016460905</v>
+      </c>
+      <c r="E38">
+        <v>232</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Tamang</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D39">
+        <v>5.37037037037037</v>
+      </c>
+      <c r="E39">
+        <v>59</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tharu</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D40">
+        <v>5.608815426997245</v>
+      </c>
+      <c r="E40">
+        <v>724</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Bhojpuri</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>4.852474323062558</v>
+      </c>
+      <c r="E41">
+        <v>39</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Maithili</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>4.761939879196516</v>
+      </c>
+      <c r="E42">
+        <v>493</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Nepali</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>5.528672973117417</v>
+      </c>
+      <c r="E43">
+        <v>2715</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Newari</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>6.25</v>
+      </c>
+      <c r="E44">
+        <v>357</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>5.031821617535903</v>
+      </c>
+      <c r="E45">
+        <v>232</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Tamang</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>5.296296296296296</v>
+      </c>
+      <c r="E46">
+        <v>59</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Tharu</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D47">
+        <v>5.576267905536198</v>
+      </c>
+      <c r="E47">
+        <v>724</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Awadi</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>7.089230084557187</v>
+      </c>
+      <c r="E48">
+        <v>332</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Bhojpuri</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D49">
+        <v>4.463369963369964</v>
+      </c>
+      <c r="E49">
+        <v>39</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D50">
+        <v>6.462585034013605</v>
+      </c>
+      <c r="E50">
+        <v>7</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Maithili</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D51">
+        <v>4.790244708994709</v>
+      </c>
+      <c r="E51">
+        <v>493</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Nepali</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D52">
+        <v>5.540877017991059</v>
+      </c>
+      <c r="E52">
+        <v>2715</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Newari</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D53">
+        <v>5.378260869565217</v>
+      </c>
+      <c r="E53">
+        <v>357</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D54">
+        <v>5.516891417333895</v>
+      </c>
+      <c r="E54">
+        <v>232</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Tamang</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D55">
+        <v>4.390799529688418</v>
+      </c>
+      <c r="E55">
+        <v>59</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Tharu</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D56">
+        <v>6.161785263347763</v>
+      </c>
+      <c r="E56">
+        <v>724</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Awadi</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D57">
+        <v>7.146725566536887</v>
+      </c>
+      <c r="E57">
+        <v>332</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Bhojpuri</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D58">
+        <v>4.819495319495319</v>
+      </c>
+      <c r="E58">
+        <v>39</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D59">
+        <v>6.587301587301587</v>
+      </c>
+      <c r="E59">
+        <v>7</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Maithili</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D60">
+        <v>4.791430559697782</v>
+      </c>
+      <c r="E60">
+        <v>493</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Nepali</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D61">
+        <v>5.656369085848854</v>
+      </c>
+      <c r="E61">
+        <v>2715</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Newari</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D62">
+        <v>5.500901875901875</v>
+      </c>
+      <c r="E62">
+        <v>357</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D63">
+        <v>5.418914173338952</v>
+      </c>
+      <c r="E63">
+        <v>232</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Tamang</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D64">
+        <v>4.577460317460317</v>
+      </c>
+      <c r="E64">
+        <v>59</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Main
+language</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Tharu</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D65">
+        <v>6.104396482813748</v>
+      </c>
+      <c r="E65">
+        <v>724</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Main language</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>18-39</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D66">
+        <v>5.638024357239512</v>
+      </c>
+      <c r="E66">
+        <v>2537</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>40-59</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D67">
+        <v>5.395472582972583</v>
+      </c>
+      <c r="E67">
+        <v>1765</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>60+</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D68">
+        <v>5.119017894298793</v>
+      </c>
+      <c r="E68">
+        <v>656</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>18-39</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D69">
+        <v>5.507047355595073</v>
+      </c>
+      <c r="E69">
+        <v>2537</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>40-59</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D70">
+        <v>5.189521717528307</v>
+      </c>
+      <c r="E70">
+        <v>1765</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>60+</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D71">
+        <v>4.836169955941819</v>
+      </c>
+      <c r="E71">
+        <v>656</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>18-39</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D72">
+        <v>5.859785141415311</v>
+      </c>
+      <c r="E72">
+        <v>2537</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>40-59</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D73">
+        <v>5.545283392786365</v>
+      </c>
+      <c r="E73">
+        <v>1765</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>60+</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D74">
+        <v>4.915134370579914</v>
+      </c>
+      <c r="E74">
+        <v>656</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>18-39</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D75">
+        <v>5.872601710587147</v>
+      </c>
+      <c r="E75">
+        <v>2537</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>40-59</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D76">
+        <v>5.636187098953056</v>
+      </c>
+      <c r="E76">
+        <v>1765</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>60+</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D77">
+        <v>5.1239929807769</v>
+      </c>
+      <c r="E77">
+        <v>656</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D78">
+        <v>5.398454746136865</v>
+      </c>
+      <c r="E78">
+        <v>2434</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D79">
+        <v>5.512509622786759</v>
+      </c>
+      <c r="E79">
+        <v>2519</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D80">
+        <v>7.222222222222221</v>
+      </c>
+      <c r="E80">
+        <v>5</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D81">
+        <v>5.17063492063492</v>
+      </c>
+      <c r="E81">
+        <v>2434</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D82">
+        <v>5.367144904073391</v>
+      </c>
+      <c r="E82">
+        <v>2519</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D83">
+        <v>4.722222222222221</v>
+      </c>
+      <c r="E83">
+        <v>5</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D84">
+        <v>5.606181835500309</v>
+      </c>
+      <c r="E84">
+        <v>2434</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D85">
+        <v>5.651128303050585</v>
+      </c>
+      <c r="E85">
+        <v>2519</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D86">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="E86">
+        <v>5</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D87">
+        <v>5.630489134137203</v>
+      </c>
+      <c r="E87">
+        <v>2434</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D88">
+        <v>5.757085350951139</v>
+      </c>
+      <c r="E88">
+        <v>2519</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D89">
+        <v>4.761904761904761</v>
+      </c>
+      <c r="E89">
+        <v>5</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>No formal education</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D90">
+        <v>5.050014581510644</v>
+      </c>
+      <c r="E90">
+        <v>791</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Primary School</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D91">
+        <v>5.390323903239032</v>
+      </c>
+      <c r="E91">
+        <v>1362</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Secondary School</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D92">
+        <v>5.67915309446254</v>
+      </c>
+      <c r="E92">
+        <v>1956</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D93">
+        <v>6.16797385620915</v>
+      </c>
+      <c r="E93">
+        <v>849</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>No formal education</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D94">
+        <v>4.627931455517662</v>
+      </c>
+      <c r="E94">
+        <v>791</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Primary School</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D95">
+        <v>5.26665169212339</v>
+      </c>
+      <c r="E95">
+        <v>1362</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Secondary School</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D96">
+        <v>5.594671201814059</v>
+      </c>
+      <c r="E96">
+        <v>1956</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D97">
+        <v>5.946428571428571</v>
+      </c>
+      <c r="E97">
+        <v>849</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>No formal education</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D98">
+        <v>4.82766439909297</v>
+      </c>
+      <c r="E98">
+        <v>791</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Primary School</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D99">
+        <v>5.483174360467938</v>
+      </c>
+      <c r="E99">
+        <v>1362</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Secondary School</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D100">
+        <v>5.800927665472641</v>
+      </c>
+      <c r="E100">
+        <v>1956</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D101">
+        <v>6.137534568322158</v>
+      </c>
+      <c r="E101">
+        <v>849</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>No formal education</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D102">
+        <v>5.045606494746895</v>
+      </c>
+      <c r="E102">
+        <v>791</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Primary School</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D103">
+        <v>5.612181475399866</v>
+      </c>
+      <c r="E103">
+        <v>1362</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Secondary School</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D104">
+        <v>5.795039682539682</v>
+      </c>
+      <c r="E104">
+        <v>1956</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D105">
+        <v>6.134030382240406</v>
+      </c>
+      <c r="E105">
+        <v>849</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Active but unemployed</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D106">
+        <v>6.082977207977208</v>
+      </c>
+      <c r="E106">
+        <v>357</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Employed</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D107">
+        <v>5.528468238793287</v>
+      </c>
+      <c r="E107">
+        <v>3344</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Not economically active</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D108">
+        <v>4.938905180840664</v>
+      </c>
+      <c r="E108">
+        <v>884</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Not usually active</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D109">
+        <v>5.582278481012658</v>
+      </c>
+      <c r="E109">
+        <v>373</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Active but unemployed</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D110">
+        <v>6.032842522974102</v>
+      </c>
+      <c r="E110">
+        <v>357</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Employed</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D111">
+        <v>5.283133181867359</v>
+      </c>
+      <c r="E111">
+        <v>3344</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Not economically active</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D112">
+        <v>4.903766879886282</v>
+      </c>
+      <c r="E112">
+        <v>884</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Not usually active</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D113">
+        <v>5.291340164757885</v>
+      </c>
+      <c r="E113">
+        <v>373</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Active but unemployed</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D114">
+        <v>5.886657464918335</v>
+      </c>
+      <c r="E114">
+        <v>357</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Employed</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D115">
+        <v>5.652290080105885</v>
+      </c>
+      <c r="E115">
+        <v>3344</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Not economically active</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D116">
+        <v>5.326399633258839</v>
+      </c>
+      <c r="E116">
+        <v>884</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Not usually active</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D117">
+        <v>5.858167626024769</v>
+      </c>
+      <c r="E117">
+        <v>373</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Active but unemployed</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D118">
+        <v>5.885553255118472</v>
+      </c>
+      <c r="E118">
+        <v>357</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Employed</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D119">
+        <v>5.740328925260432</v>
+      </c>
+      <c r="E119">
+        <v>3344</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Not economically active</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D120">
+        <v>5.395188611015949</v>
+      </c>
+      <c r="E120">
+        <v>884</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Not usually active</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D121">
+        <v>5.795903045903046</v>
+      </c>
+      <c r="E121">
+        <v>373</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Born in
+Nepal</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D122">
+        <v>4.991111111111111</v>
+      </c>
+      <c r="E122">
+        <v>61</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Born in Nepal</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Born in
+Nepal</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D123">
+        <v>5.467821609963125</v>
+      </c>
+      <c r="E123">
+        <v>4897</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Born in Nepal</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Born in
+Nepal</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D124">
+        <v>4.254603174603174</v>
+      </c>
+      <c r="E124">
+        <v>61</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Born in Nepal</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Born in
+Nepal</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D125">
+        <v>5.291570497246517</v>
+      </c>
+      <c r="E125">
+        <v>4897</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Born in Nepal</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Born in
+Nepal</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D126">
+        <v>5.236424394319131</v>
+      </c>
+      <c r="E126">
+        <v>61</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Born in Nepal</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Born in
+Nepal</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D127">
+        <v>5.632849066104335</v>
+      </c>
+      <c r="E127">
+        <v>4897</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Born in Nepal</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Born in
+Nepal</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D128">
+        <v>5.582238642583469</v>
+      </c>
+      <c r="E128">
+        <v>61</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Born in Nepal</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Born in
+Nepal</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D129">
+        <v>5.696099078939818</v>
+      </c>
+      <c r="E129">
+        <v>4897</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Born in Nepal</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Disabilities</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D130">
+        <v>5.461687376193049</v>
+      </c>
+      <c r="E130">
+        <v>3814</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Disabilities</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D131">
+        <v>5.456615120274914</v>
+      </c>
+      <c r="E131">
+        <v>1144</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Disabilities</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D132">
+        <v>5.346213679270157</v>
+      </c>
+      <c r="E132">
+        <v>3814</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Disabilities</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D133">
+        <v>5.055800383563879</v>
+      </c>
+      <c r="E133">
+        <v>1144</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Disabilities</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D134">
+        <v>5.781436113495097</v>
+      </c>
+      <c r="E134">
+        <v>3814</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Disabilities</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D135">
+        <v>5.113872899587185</v>
+      </c>
+      <c r="E135">
+        <v>1144</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Disabilities</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D136">
+        <v>5.825342967443945</v>
+      </c>
+      <c r="E136">
+        <v>3814</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Disabilities</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D137">
+        <v>5.247874018069004</v>
+      </c>
+      <c r="E137">
+        <v>1144</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Received
+early
+warnings
+from NS</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D138">
+        <v>5.046116812365387</v>
+      </c>
+      <c r="E138">
+        <v>2327</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Did you personally receive the warning(s) by Nepal Red Cross?</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Received
+early
+warnings
+from NS</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D139">
+        <v>6.536443494776828</v>
+      </c>
+      <c r="E139">
+        <v>1971</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Did you personally receive the warning(s) by Nepal Red Cross?</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Received
+early
+warnings
+from NS</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D140">
+        <v>4.842112574317942</v>
+      </c>
+      <c r="E140">
+        <v>2327</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Did you personally receive the warning(s) by Nepal Red Cross?</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Received
+early
+warnings
+from NS</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D141">
+        <v>6.286780383795309</v>
+      </c>
+      <c r="E141">
+        <v>1971</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Did you personally receive the warning(s) by Nepal Red Cross?</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Received
+early
+warnings
+from NS</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D142">
+        <v>4.801121478305944</v>
+      </c>
+      <c r="E142">
+        <v>2327</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Did you personally receive the warning(s) by Nepal Red Cross?</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Received
+early
+warnings
+from NS</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D143">
+        <v>6.845318750806555</v>
+      </c>
+      <c r="E143">
+        <v>1971</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Did you personally receive the warning(s) by Nepal Red Cross?</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Received
+early
+warnings
+from NS</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D144">
+        <v>5.020067220245156</v>
+      </c>
+      <c r="E144">
+        <v>2327</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Did you personally receive the warning(s) by Nepal Red Cross?</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Received
+early
+warnings
+from NS</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D145">
+        <v>6.724875802738397</v>
+      </c>
+      <c r="E145">
+        <v>1971</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Did you personally receive the warning(s) by Nepal Red Cross?</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Once
+beneficiary</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D146">
+        <v>5.080079141934812</v>
+      </c>
+      <c r="E146">
+        <v>2989</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Have been ever received aid or support</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Once
+beneficiary</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="D147">
+        <v>6.191791791791792</v>
+      </c>
+      <c r="E147">
+        <v>1969</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Have been ever received aid or support</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Once
+beneficiary</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D148">
+        <v>4.89719240297275</v>
+      </c>
+      <c r="E148">
+        <v>2989</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Have been ever received aid or support</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Once
+beneficiary</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D149">
+        <v>5.982453882453882</v>
+      </c>
+      <c r="E149">
+        <v>1969</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Have been ever received aid or support</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Once
+beneficiary</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D150">
+        <v>5.180035485482956</v>
+      </c>
+      <c r="E150">
+        <v>2989</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Have been ever received aid or support</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Once
+beneficiary</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D151">
+        <v>6.285421866376718</v>
+      </c>
+      <c r="E151">
+        <v>1969</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Have been ever received aid or support</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Once
+beneficiary</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D152">
+        <v>5.290528690950929</v>
+      </c>
+      <c r="E152">
+        <v>2989</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Have been ever received aid or support</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Once
+beneficiary</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D153">
+        <v>6.293299254737503</v>
+      </c>
+      <c r="E153">
+        <v>1969</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Have been ever received aid or support</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2764,49 +8659,142 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Age Group</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Total Respondents</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Percentage (%)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aid recipient</t>
+          <t>18-39</t>
         </is>
       </c>
       <c r="B2">
-        <v>1401</v>
+        <v>2537</v>
+      </c>
+      <c r="C2">
+        <v>51.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Volunteer</t>
+          <t>40-59</t>
         </is>
       </c>
       <c r="B3">
-        <v>495</v>
+        <v>1765</v>
+      </c>
+      <c r="C3">
+        <v>35.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="B4">
-        <v>1699</v>
+        <v>656</v>
+      </c>
+      <c r="C4">
+        <v>13.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Total Respondents</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Percentage (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>2434</v>
+      </c>
+      <c r="C2">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>2519</v>
+      </c>
+      <c r="C3">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Other or did not answer</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>4958</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
